--- a/KazApi_document/設計書.xlsx
+++ b/KazApi_document/設計書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\KazApp\KazApi_document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository_kaz_app\kaz_app\KazApi_document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9ECB3DD-E2AA-44F9-9A6E-B485BAF8F3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D1DF87-B0EB-497A-B987-2361882C4EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-28785" yWindow="-15" windowWidth="28770" windowHeight="15495" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="15" yWindow="0" windowWidth="28770" windowHeight="15495" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
@@ -7661,220 +7661,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>308885</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>78923</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>496774</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="128" name="グループ化 127">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D54C2ED-7E4D-7DEB-7953-CBA163118923}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="3726679" y="7642894"/>
-          <a:ext cx="2238566" cy="1601960"/>
-          <a:chOff x="3595464" y="7579840"/>
-          <a:chExt cx="2256175" cy="1641481"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="125" name="正方形/長方形 124">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43A6B964-20D8-4E10-2DF9-AF0639421DF3}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3705886" y="7579840"/>
-            <a:ext cx="2145753" cy="1641481"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="bg1">
-              <a:lumMod val="65000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="28575">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-              <a:t>所持アイテム</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-          </a:p>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-              <a:t>===============</a:t>
-            </a:r>
-          </a:p>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-              <a:t>ログイン</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-              <a:t>ID</a:t>
-            </a:r>
-          </a:p>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-              <a:t>アイテム</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-              <a:t>ID [ ] </a:t>
-            </a:r>
-          </a:p>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-              <a:t>購入日</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-          </a:p>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-              <a:t>有効無効</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-          </a:p>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-              <a:t>...</a:t>
-            </a:r>
-          </a:p>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-              <a:t>=================</a:t>
-            </a:r>
-          </a:p>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-          </a:p>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="126" name="ひし形 125">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A05C25B-F6CA-8D99-477C-468FA0B4212F}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3595464" y="7878976"/>
-            <a:ext cx="247833" cy="240408"/>
-          </a:xfrm>
-          <a:prstGeom prst="diamond">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>165902</xdr:colOff>
       <xdr:row>35</xdr:row>
@@ -7924,6 +7710,723 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>165902</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>166848</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>11206</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>145034</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="直線コネクタ 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F325A091-E416-4008-BD2C-AE36C1C2A342}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="12" idx="1"/>
+          <a:endCxn id="10" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2900137" y="5545672"/>
+          <a:ext cx="3946657" cy="482450"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>11206</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>425823</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>134471</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="18" name="グループ化 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8FC1ADC-15FC-DF5E-AD1C-651A6FBAD653}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6846794" y="5210735"/>
+          <a:ext cx="1781735" cy="1311089"/>
+          <a:chOff x="6846794" y="5210735"/>
+          <a:chExt cx="2341399" cy="1311089"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="7" name="グループ化 6">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB5720DA-ED11-4FA5-ACDE-E30E17E7DFBF}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="6846794" y="5210735"/>
+            <a:ext cx="2238566" cy="1311089"/>
+            <a:chOff x="3595464" y="7579840"/>
+            <a:chExt cx="2256175" cy="1641481"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="11" name="正方形/長方形 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1EBF794-BECC-1D3A-06A8-952B681E23D0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3705886" y="7579840"/>
+              <a:ext cx="2145753" cy="1641481"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="65000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+                <a:t>利用可能店舗</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+                <a:t>===============</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+                <a:t>ログイン</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+                <a:t>ID</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+                <a:t>ショップ</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+                <a:t>ID</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+                <a:t>...</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+                <a:t>=================</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="12" name="ひし形 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2491992D-EC87-105E-8C2D-A1835A32DA97}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3595464" y="7878976"/>
+              <a:ext cx="247833" cy="240408"/>
+            </a:xfrm>
+            <a:prstGeom prst="diamond">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="17" name="ひし形 16">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96668046-94D6-4A8F-A89E-F46239B83F7C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8942294" y="5345206"/>
+            <a:ext cx="245899" cy="192019"/>
+          </a:xfrm>
+          <a:prstGeom prst="diamond">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>425823</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>7351</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>344605</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>62392</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="直線コネクタ 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F887C88-EE3B-41B8-8679-4A72EE0F90FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="56" idx="1"/>
+          <a:endCxn id="17" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="8628529" y="4041469"/>
+          <a:ext cx="2653017" cy="1399747"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>593280</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>72486</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>10042</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>115949</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="23" name="直線コネクタ 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A4FC1DD-8F86-4CAB-A236-D5414E0CD0B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="37" idx="1"/>
+          <a:endCxn id="27" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="6061751" y="7972633"/>
+          <a:ext cx="4885232" cy="547728"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>308885</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>78923</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>593280</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="28" name="グループ化 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2BD7EB6-6F1D-7407-99A1-546515853FB5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="3726679" y="7642894"/>
+          <a:ext cx="2335072" cy="1601960"/>
+          <a:chOff x="3726679" y="7642894"/>
+          <a:chExt cx="2335072" cy="1601960"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="128" name="グループ化 127">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D54C2ED-7E4D-7DEB-7953-CBA163118923}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="3726679" y="7642894"/>
+            <a:ext cx="2238566" cy="1601960"/>
+            <a:chOff x="3595464" y="7579840"/>
+            <a:chExt cx="2256175" cy="1641481"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="125" name="正方形/長方形 124">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43A6B964-20D8-4E10-2DF9-AF0639421DF3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3705886" y="7579840"/>
+              <a:ext cx="2145753" cy="1641481"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="65000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+                <a:t>所持アイテム</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+                <a:t>===============</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+                <a:t>ログイン</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+                <a:t>ID</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+                <a:t>アイテム</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+                <a:t>ID [ ] </a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+                <a:t>購入日</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+                <a:t>有効無効</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+                <a:t>...</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+                <a:t>=================</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="126" name="ひし形 125">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A05C25B-F6CA-8D99-477C-468FA0B4212F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3595464" y="7878976"/>
+              <a:ext cx="247833" cy="240408"/>
+            </a:xfrm>
+            <a:prstGeom prst="diamond">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="27" name="ひし形 26">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2F855DE-9C15-4193-B2D2-23BC641B43F9}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5815852" y="7855323"/>
+            <a:ext cx="245899" cy="234620"/>
+          </a:xfrm>
+          <a:prstGeom prst="diamond">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
